--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486680_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486680_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>J. GARCIA CABRERA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5386</v>
+        <v>4.8218</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3414</v>
+        <v>1.3882</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1972</v>
+        <v>3.4336</v>
       </c>
       <c r="G2" t="n">
-        <v>0.956</v>
+        <v>3.3155</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6757</v>
+        <v>1.4617</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2803</v>
+        <v>1.8537</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9024</v>
+        <v>1.4544</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4698</v>
+        <v>1.5312</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5674</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9464</v>
+        <v>1.861</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7941</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8477</v>
+        <v>1.9305</v>
       </c>
       <c r="P2" t="n">
         <v>1.1585</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3169</v>
+        <v>-0.3862</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4754</v>
+        <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.0622</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0004</v>
+        <v>0.0344</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6682</v>
+        <v>0.0279</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7563</v>
+        <v>0.2856</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7563</v>
+        <v>0.2856</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4664</v>
+        <v>4.3192</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4542</v>
+        <v>1.4448</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0122</v>
+        <v>2.8744</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8908</v>
+        <v>0.956</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5036</v>
+        <v>0.6757</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3872</v>
+        <v>0.2803</v>
       </c>
       <c r="J3" t="n">
-        <v>6.5957</v>
+        <v>1.9024</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6425</v>
+        <v>2.4698</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9532</v>
+        <v>-0.5674</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7049</v>
+        <v>-0.9464</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.1389</v>
+        <v>-1.7941</v>
       </c>
       <c r="O3" t="n">
-        <v>0.434</v>
+        <v>0.8477</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.7031</v>
+        <v>1.1585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6.1785</v>
+        <v>-2.3169</v>
       </c>
       <c r="R3" t="n">
         <v>3.4754</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3793</v>
+        <v>0.4484</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9099</v>
+        <v>0.1031</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4694</v>
+        <v>0.3454</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8995</v>
+        <v>1.7563</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1271</v>
+        <v>1.7563</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GARCIA CABRERA</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1142</v>
+        <v>4.032</v>
       </c>
       <c r="E4" t="n">
-        <v>1.078</v>
+        <v>3.1439</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0362</v>
+        <v>0.8881</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3155</v>
+        <v>4.8908</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4617</v>
+        <v>2.5036</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8537</v>
+        <v>2.3872</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4544</v>
+        <v>6.5957</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5312</v>
+        <v>4.6425</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.07679999999999999</v>
+        <v>1.9532</v>
       </c>
       <c r="M4" t="n">
-        <v>1.861</v>
+        <v>-1.7049</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-2.1389</v>
       </c>
       <c r="O4" t="n">
-        <v>1.9305</v>
+        <v>0.434</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3862</v>
+        <v>-6.1785</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5446</v>
+        <v>3.4754</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6453</v>
+        <v>0.9448</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2759</v>
+        <v>0.5996</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3694</v>
+        <v>0.3452</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2856</v>
+        <v>0.8995</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2856</v>
+        <v>2.1271</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4113</v>
+        <v>3.25</v>
       </c>
       <c r="E5" t="n">
-        <v>4.058</v>
+        <v>3.7477</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.4977</v>
       </c>
       <c r="G5" t="n">
         <v>1.9949</v>
@@ -844,13 +844,13 @@
         <v>1.9308</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4856</v>
+        <v>0.3243</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4688</v>
+        <v>0.1585</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0169</v>
+        <v>0.1658</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6138</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>A. OMERAGIC ALIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7958</v>
+        <v>1.8138</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6413</v>
+        <v>1.0211</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1545</v>
+        <v>0.7927</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0897</v>
+        <v>-0.1108</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9518</v>
+        <v>0.1583</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1379</v>
+        <v>-0.269</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9518</v>
+        <v>-0.6688</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9518</v>
+        <v>0.0207</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6895</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1379</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.1376</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1379</v>
+        <v>0.4205</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>0.706</v>
+        <v>0.0484</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6895</v>
+        <v>0.1999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0166</v>
+        <v>-0.1515</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. OMERAGIC ALIC</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3187</v>
+        <v>1.4069</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6005</v>
+        <v>1.2276</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.1793</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1108</v>
+        <v>1.0897</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1583</v>
+        <v>0.9518</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.269</v>
+        <v>0.1379</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6688</v>
+        <v>0.9518</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0207</v>
+        <v>0.9518</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6895</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.1379</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1376</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4205</v>
+        <v>0.1379</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4467</v>
+        <v>0.3172</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2207</v>
+        <v>0.2758</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.226</v>
+        <v>0.0414</v>
       </c>
       <c r="V7" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0593</v>
+        <v>1.1489</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5641</v>
+        <v>-0.3503</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6234</v>
+        <v>1.4992</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0301</v>
@@ -1078,13 +1078,13 @@
         <v>2.51</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1933</v>
+        <v>0.2829</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0004</v>
+        <v>0.2134</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1936</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6232</v>
+        <v>0.3474</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0176</v>
+        <v>-1.1693</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6409</v>
+        <v>1.5167</v>
       </c>
       <c r="G9" t="n">
         <v>0.4025</v>
@@ -1156,13 +1156,13 @@
         <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4139</v>
+        <v>0.138</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3032</v>
+        <v>0.1515</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1107</v>
+        <v>-0.0135</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. CAMPOS RODRIGUEZ</t>
+          <t>J. ORAMAS MARTEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2357</v>
+        <v>0.337</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.724</v>
+        <v>1.0371</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4883</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3241</v>
+        <v>0.3054</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0896</v>
+        <v>-0.5243</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4137</v>
+        <v>0.8297</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6688</v>
+        <v>1.5268</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0207</v>
+        <v>0.3037</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6895</v>
+        <v>1.2231</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3447</v>
+        <v>-1.2214</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0689</v>
+        <v>-0.828</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2758</v>
+        <v>-0.3934</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08840000000000001</v>
+        <v>-0.4551</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0552</v>
+        <v>-0.1381</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1436</v>
+        <v>-0.317</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ORAMAS MARTEL</t>
+          <t>G. CAMPOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4106</v>
+        <v>-0.2758</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5131</v>
+        <v>-0.5654</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9236</v>
+        <v>0.2896</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3054</v>
+        <v>-0.3241</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5243</v>
+        <v>0.0896</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8297</v>
+        <v>-0.4137</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5268</v>
+        <v>-0.6688</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3037</v>
+        <v>0.0207</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2231</v>
+        <v>-0.6895</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2214</v>
+        <v>0.3447</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.828</v>
+        <v>0.0689</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3934</v>
+        <v>0.2758</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2027</v>
+        <v>0.0484</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6622</v>
+        <v>0.1034</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5405</v>
+        <v>-0.0551</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3152</v>
+        <v>-1.1318</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1103</v>
+        <v>0.2689</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4255</v>
+        <v>-1.4007</v>
       </c>
       <c r="G12" t="n">
         <v>0.2473</v>
@@ -1390,13 +1390,13 @@
         <v>0.1931</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1764</v>
+        <v>0.007</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1932</v>
+        <v>-0.0346</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0168</v>
+        <v>0.0416</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6138</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.1843</v>
+        <v>-7.3359</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.8558</v>
+        <v>-8.0075</v>
       </c>
       <c r="F13" t="n">
         <v>0.6715</v>
@@ -1468,10 +1468,10 @@
         <v>3.2823</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7448</v>
+        <v>0.5931</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6891</v>
+        <v>0.5375</v>
       </c>
       <c r="U13" t="n">
         <v>0.0557</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.1817</v>
+        <v>12.7335</v>
       </c>
       <c r="E14" t="n">
-        <v>2.635299999999999</v>
+        <v>3.186800000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>9.546600000000002</v>
+        <v>9.5466</v>
       </c>
       <c r="G14" t="n">
         <v>8.963200000000001</v>
@@ -1525,7 +1525,7 @@
         <v>13.1095</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8247999999999998</v>
+        <v>-0.8247999999999995</v>
       </c>
       <c r="M14" t="n">
         <v>-3.3215</v>
@@ -1546,13 +1546,13 @@
         <v>19.3078</v>
       </c>
       <c r="S14" t="n">
-        <v>2.208</v>
+        <v>2.759600000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6525</v>
+        <v>2.2044</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5555999999999999</v>
+        <v>0.5553999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>2.9415</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.263</v>
+        <v>3.2218</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8951</v>
+        <v>1.9643</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3679</v>
+        <v>1.2575</v>
       </c>
       <c r="G15" t="n">
         <v>0.6919</v>
@@ -1624,13 +1624,13 @@
         <v>2.7031</v>
       </c>
       <c r="S15" t="n">
-        <v>1.048</v>
+        <v>0.0068</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1579</v>
+        <v>0.2271</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1099</v>
+        <v>-0.2203</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1799</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3271</v>
+        <v>2.8731</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6126</v>
+        <v>1.2331</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7145</v>
+        <v>1.64</v>
       </c>
       <c r="G16" t="n">
         <v>2.7221</v>
@@ -1702,13 +1702,13 @@
         <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9874000000000001</v>
+        <v>-0.4414</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9381</v>
+        <v>-0.3176</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0493</v>
+        <v>-0.1238</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1799</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>K. RYTZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9305</v>
+        <v>0.3558</v>
       </c>
       <c r="E17" t="n">
-        <v>1.56</v>
+        <v>-0.1723</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6294</v>
+        <v>0.5281</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0732</v>
+        <v>-0.0619</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8893</v>
+        <v>-0.1998</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8161</v>
+        <v>0.1379</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1158</v>
+        <v>-0.3377</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9937</v>
+        <v>-0.3377</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1221</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0426</v>
+        <v>0.2758</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1044</v>
+        <v>0.1379</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9382</v>
+        <v>0.1379</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3169</v>
+        <v>0.3862</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5738</v>
+        <v>0.3172</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4409</v>
+        <v>0.1654</v>
       </c>
       <c r="U17" t="n">
-        <v>0.133</v>
+        <v>0.1518</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1373</v>
+        <v>-0.2856</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0367</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. RYTZ</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.844</v>
+        <v>0.0257</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2414</v>
+        <v>0.9394</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6026</v>
+        <v>-0.9137</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0619</v>
+        <v>1.0732</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1998</v>
+        <v>1.8893</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1379</v>
+        <v>-0.8161</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3377</v>
+        <v>3.1158</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3377</v>
+        <v>2.9937</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1221</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2758</v>
+        <v>-2.0426</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1379</v>
+        <v>-1.1044</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1379</v>
+        <v>-0.9382</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3862</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3862</v>
+        <v>2.3169</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8054</v>
+        <v>-0.3309</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5790999999999999</v>
+        <v>-0.1797</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2262</v>
+        <v>-0.1513</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2856</v>
+        <v>-0.1373</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>-1.0367</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0307</v>
+        <v>-1.1867</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3938</v>
+        <v>-2.7733</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3631</v>
+        <v>1.5866</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6223</v>
@@ -1936,13 +1936,13 @@
         <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8718</v>
+        <v>-0.0278</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7175</v>
+        <v>-0.097</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1543</v>
+        <v>0.0692</v>
       </c>
       <c r="V19" t="n">
         <v>0.6565</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>A. LOPEZ ROMERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5374</v>
+        <v>-2.0756</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3792</v>
+        <v>-1.1085</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1581</v>
+        <v>-0.9671</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0688</v>
+        <v>-1.9093</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8337</v>
+        <v>-2.2213</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2351</v>
+        <v>0.312</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0683</v>
+        <v>0.9053</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7301</v>
+        <v>0.3311</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3383</v>
+        <v>0.5743</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0005</v>
+        <v>-2.8147</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1036</v>
+        <v>-2.5524</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1032</v>
+        <v>-0.2623</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1931</v>
+        <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9209000000000001</v>
+        <v>-0.1795</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8822</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0387</v>
+        <v>-0.0964</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.741</v>
+        <v>-0.1799</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.741</v>
+        <v>-0.1799</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LOPEZ ROMERA</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7513</v>
+        <v>-2.9552</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5222</v>
+        <v>-1.8963</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2291</v>
+        <v>-1.0588</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9093</v>
+        <v>-2.0688</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2213</v>
+        <v>-1.8337</v>
       </c>
       <c r="I21" t="n">
-        <v>0.312</v>
+        <v>-0.2351</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9053</v>
+        <v>-2.0683</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3311</v>
+        <v>-0.7301</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5743</v>
+        <v>-1.3383</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8147</v>
+        <v>-0.0005</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5524</v>
+        <v>-1.1036</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2623</v>
+        <v>1.1032</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>-0.1931</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8552</v>
+        <v>0.5031</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4968</v>
+        <v>0.3651</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3584</v>
+        <v>0.138</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1799</v>
+        <v>-2.741</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1799</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4495</v>
+        <v>-3.7101</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.3919</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3678</v>
+        <v>-3.3181</v>
       </c>
       <c r="G22" t="n">
         <v>0.5723</v>
@@ -2170,13 +2170,13 @@
         <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>0.419</v>
+        <v>0.1584</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4135</v>
+        <v>0.1032</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0056</v>
+        <v>0.0552</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>J. MEJIA ECHEVERRY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7406</v>
+        <v>-3.9474</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0164</v>
+        <v>-3.8625</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2759</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8414</v>
+        <v>-5.5189</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5246</v>
+        <v>-2.7519</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.366</v>
+        <v>-2.767</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8954</v>
+        <v>-2.2346</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6288</v>
+        <v>-0.13</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.5242</v>
+        <v>-2.1046</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-3.2843</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1043</v>
+        <v>-2.6219</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1582</v>
+        <v>-0.6624</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7723</v>
+        <v>2.51</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.0546</v>
+        <v>-1.1585</v>
       </c>
       <c r="R23" t="n">
-        <v>3.2823</v>
+        <v>3.6685</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4124</v>
+        <v>-0.7587</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5797</v>
+        <v>-0.4695</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8327</v>
+        <v>-0.2892</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2856</v>
+        <v>-0.1799</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2277</v>
+        <v>-0.1799</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MEJIA ECHEVERRY</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0369</v>
+        <v>-4.0938</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6899</v>
+        <v>-4.7062</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.347</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.5189</v>
+        <v>-2.8414</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7519</v>
+        <v>0.5246</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.767</v>
+        <v>-3.366</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2346</v>
+        <v>-1.8954</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.13</v>
+        <v>1.6288</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.1046</v>
+        <v>-3.5242</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2843</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.6219</v>
+        <v>-1.1043</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6624</v>
+        <v>0.1582</v>
       </c>
       <c r="P24" t="n">
-        <v>2.51</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1585</v>
+        <v>-4.0546</v>
       </c>
       <c r="R24" t="n">
-        <v>3.6685</v>
+        <v>3.2823</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8481</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2968</v>
+        <v>-0.2694</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5513</v>
+        <v>-0.4962</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1799</v>
+        <v>0.2856</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1799</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.1818</v>
+        <v>-11.4924</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.7741</v>
+        <v>-10.7742</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4074</v>
+        <v>-0.7181000000000002</v>
       </c>
       <c r="G25" t="n">
         <v>-8.963100000000001</v>
@@ -2392,10 +2392,10 @@
         <v>-13.1094</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8248000000000001</v>
+        <v>0.8248000000000002</v>
       </c>
       <c r="P25" t="n">
-        <v>1.9308</v>
+        <v>1.930799999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-19.3079</v>
@@ -2404,13 +2404,13 @@
         <v>21.2386</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.2078</v>
+        <v>-1.5184</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5553000000000002</v>
+        <v>-0.5554999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6524</v>
+        <v>-0.963</v>
       </c>
       <c r="V25" t="n">
         <v>-2.9414</v>
